--- a/artfynd/A 14286-2026 artfynd.xlsx
+++ b/artfynd/A 14286-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132880784</v>
+        <v>132880032</v>
       </c>
       <c r="B3" t="n">
         <v>99130</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758703</v>
+        <v>758820</v>
       </c>
       <c r="R3" t="n">
-        <v>7176533</v>
+        <v>7176502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132880032</v>
+        <v>132880784</v>
       </c>
       <c r="B4" t="n">
         <v>99130</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758820</v>
+        <v>758703</v>
       </c>
       <c r="R4" t="n">
-        <v>7176502</v>
+        <v>7176533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132879260</v>
+        <v>132879927</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,27 +1648,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758902</v>
+        <v>758851</v>
       </c>
       <c r="R11" t="n">
-        <v>7176510</v>
+        <v>7176509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132879887</v>
+        <v>132879260</v>
       </c>
       <c r="B12" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758850</v>
+        <v>758902</v>
       </c>
       <c r="R12" t="n">
-        <v>7176516</v>
+        <v>7176510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,42 +1847,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132881159</v>
+        <v>132879887</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>83181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1890,10 +1889,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758818</v>
+        <v>758850</v>
       </c>
       <c r="R13" t="n">
-        <v>7176529</v>
+        <v>7176516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,41 +1952,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132879927</v>
+        <v>132881159</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758851</v>
+        <v>758818</v>
       </c>
       <c r="R14" t="n">
-        <v>7176509</v>
+        <v>7176529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,32 +2168,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132879094</v>
+        <v>132880293</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>92378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758950</v>
+        <v>758718</v>
       </c>
       <c r="R16" t="n">
-        <v>7176530</v>
+        <v>7176498</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,6 +2246,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,42 +2278,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132880932</v>
+        <v>132879094</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2316,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758831</v>
+        <v>758950</v>
       </c>
       <c r="R17" t="n">
-        <v>7176561</v>
+        <v>7176530</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,17 +2358,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>gammalt bohål i fallen, ihålig gran. typisk storlek och höjd över marken.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2383,41 +2383,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132880293</v>
+        <v>132880932</v>
       </c>
       <c r="B18" t="n">
-        <v>92378</v>
+        <v>57958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758718</v>
+        <v>758831</v>
       </c>
       <c r="R18" t="n">
-        <v>7176498</v>
+        <v>7176561</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2466,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>samma låga som ullticka</t>
+          <t>gammalt bohål i fallen, ihålig gran. typisk storlek och höjd över marken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2475,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132879174</v>
+        <v>132880214</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3149,27 +3149,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>758921</v>
+        <v>758739</v>
       </c>
       <c r="R25" t="n">
-        <v>7176542</v>
+        <v>7176545</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132880214</v>
+        <v>132879174</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,27 +3254,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>758739</v>
+        <v>758921</v>
       </c>
       <c r="R26" t="n">
-        <v>7176545</v>
+        <v>7176542</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132879195</v>
+        <v>132880809</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3579,30 +3579,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3610,10 +3611,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>758892</v>
+        <v>758708</v>
       </c>
       <c r="R29" t="n">
-        <v>7176540</v>
+        <v>7176532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,16 +3651,15 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>riklig förekomst med många draperade träd</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132879679</v>
+        <v>132881273</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3689,30 +3689,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3720,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>758824</v>
+        <v>758880</v>
       </c>
       <c r="R30" t="n">
-        <v>7176484</v>
+        <v>7176534</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,13 +3759,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3783,7 +3788,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132880809</v>
+        <v>132879868</v>
       </c>
       <c r="B31" t="n">
         <v>57958</v>
@@ -3816,7 +3821,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3826,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>758708</v>
+        <v>758849</v>
       </c>
       <c r="R31" t="n">
-        <v>7176532</v>
+        <v>7176524</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3866,14 +3871,14 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>bohål i gran, typisk storlek och ca 180cm över mark</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -3893,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132881273</v>
+        <v>132881068</v>
       </c>
       <c r="B32" t="n">
         <v>57958</v>
@@ -3936,10 +3941,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>758880</v>
+        <v>758820</v>
       </c>
       <c r="R32" t="n">
-        <v>7176534</v>
+        <v>7176557</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,7 +3981,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>barksprätt på gran med granticka</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4003,10 +4008,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132879868</v>
+        <v>132879195</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4014,31 +4019,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4046,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>758849</v>
+        <v>758892</v>
       </c>
       <c r="R33" t="n">
-        <v>7176524</v>
+        <v>7176540</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,7 +4090,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>bohål i gran, typisk storlek och ca 180cm över mark</t>
+          <t>riklig förekomst med många draperade träd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4095,6 +4099,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4113,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132881068</v>
+        <v>132879679</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4124,31 +4129,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4156,10 +4160,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>758820</v>
+        <v>758824</v>
       </c>
       <c r="R34" t="n">
-        <v>7176557</v>
+        <v>7176484</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4194,17 +4198,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>barksprätt på gran med granticka</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132879548</v>
+        <v>132879953</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,30 +5080,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5111,10 +5112,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>758831</v>
+        <v>758847</v>
       </c>
       <c r="R43" t="n">
-        <v>7176482</v>
+        <v>7176492</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5151,16 +5152,15 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>rik förekomst</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5179,10 +5179,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132880169</v>
+        <v>132879644</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5190,30 +5190,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5221,10 +5222,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>758769</v>
+        <v>758815</v>
       </c>
       <c r="R44" t="n">
-        <v>7176522</v>
+        <v>7176479</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5259,13 +5260,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5284,10 +5289,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132881222</v>
+        <v>132880152</v>
       </c>
       <c r="B45" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5295,30 +5300,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5326,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>758837</v>
+        <v>758776</v>
       </c>
       <c r="R45" t="n">
-        <v>7176528</v>
+        <v>7176508</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,13 +5370,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5389,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132879644</v>
+        <v>132880132</v>
       </c>
       <c r="B46" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,16 +5410,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5432,10 +5442,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>758815</v>
+        <v>758797</v>
       </c>
       <c r="R46" t="n">
-        <v>7176479</v>
+        <v>7176492</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5472,14 +5482,14 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackade i träd</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5499,10 +5509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132880132</v>
+        <v>132879548</v>
       </c>
       <c r="B47" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5510,31 +5520,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5542,10 +5551,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>758797</v>
+        <v>758831</v>
       </c>
       <c r="R47" t="n">
-        <v>7176492</v>
+        <v>7176482</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5582,7 +5591,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>hål hackade i träd</t>
+          <t>rik förekomst</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5591,6 +5600,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5609,10 +5619,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132880152</v>
+        <v>132880169</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5620,31 +5630,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5652,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>758776</v>
+        <v>758769</v>
       </c>
       <c r="R48" t="n">
-        <v>7176508</v>
+        <v>7176522</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5690,17 +5699,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5719,10 +5724,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132879953</v>
+        <v>132881222</v>
       </c>
       <c r="B49" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5730,31 +5735,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5762,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>758847</v>
+        <v>758837</v>
       </c>
       <c r="R49" t="n">
-        <v>7176492</v>
+        <v>7176528</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5800,17 +5804,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14286-2026 artfynd.xlsx
+++ b/artfynd/A 14286-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132881150</v>
+        <v>132880345</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758833</v>
+        <v>758636</v>
       </c>
       <c r="R2" t="n">
-        <v>7176533</v>
+        <v>7176527</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,42 +780,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132880032</v>
+        <v>132879260</v>
       </c>
       <c r="B3" t="n">
-        <v>99132</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758820</v>
+        <v>758902</v>
       </c>
       <c r="R3" t="n">
-        <v>7176502</v>
+        <v>7176510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,42 +885,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132880784</v>
+        <v>132879388</v>
       </c>
       <c r="B4" t="n">
-        <v>99132</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758703</v>
+        <v>758850</v>
       </c>
       <c r="R4" t="n">
-        <v>7176533</v>
+        <v>7176464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132881175</v>
+        <v>132879679</v>
       </c>
       <c r="B5" t="n">
-        <v>91920</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758814</v>
+        <v>758824</v>
       </c>
       <c r="R5" t="n">
-        <v>7176528</v>
+        <v>7176484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132879388</v>
+        <v>132879924</v>
       </c>
       <c r="B6" t="n">
-        <v>91920</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758850</v>
+        <v>758851</v>
       </c>
       <c r="R6" t="n">
-        <v>7176464</v>
+        <v>7176509</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132880196</v>
+        <v>132880214</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,31 +1211,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1245,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758775</v>
+        <v>758739</v>
       </c>
       <c r="R7" t="n">
-        <v>7176533</v>
+        <v>7176545</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,17 +1280,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132880898</v>
+        <v>132880221</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,31 +1316,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758745</v>
+        <v>758724</v>
       </c>
       <c r="R8" t="n">
-        <v>7176555</v>
+        <v>7176532</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,17 +1385,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1422,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132879462</v>
+        <v>132880262</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,31 +1421,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1465,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758832</v>
+        <v>758718</v>
       </c>
       <c r="R9" t="n">
-        <v>7176463</v>
+        <v>7176498</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,17 +1490,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1535,7 +1518,7 @@
         <v>132881147</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132879927</v>
+        <v>132881175</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,27 +1631,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1679,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758851</v>
+        <v>758814</v>
       </c>
       <c r="R11" t="n">
-        <v>7176509</v>
+        <v>7176528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132879260</v>
+        <v>132881222</v>
       </c>
       <c r="B12" t="n">
-        <v>91920</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758902</v>
+        <v>758837</v>
       </c>
       <c r="R12" t="n">
-        <v>7176510</v>
+        <v>7176528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132879887</v>
+        <v>132880293</v>
       </c>
       <c r="B13" t="n">
-        <v>83182</v>
+        <v>92406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758850</v>
+        <v>758718</v>
       </c>
       <c r="R13" t="n">
-        <v>7176516</v>
+        <v>7176498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,42 +1940,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132881159</v>
+        <v>132879887</v>
       </c>
       <c r="B14" t="n">
-        <v>99132</v>
+        <v>83222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1995,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758818</v>
+        <v>758850</v>
       </c>
       <c r="R14" t="n">
-        <v>7176529</v>
+        <v>7176516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,38 +2045,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132881300</v>
+        <v>132881237</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>92370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2100,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758875</v>
+        <v>758837</v>
       </c>
       <c r="R15" t="n">
-        <v>7176545</v>
+        <v>7176528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,7 +2127,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt på många träd</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,7 +2158,7 @@
         <v>132879094</v>
       </c>
       <c r="B16" t="n">
-        <v>91883</v>
+        <v>91937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,32 +2260,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132880293</v>
+        <v>132879278</v>
       </c>
       <c r="B17" t="n">
-        <v>92380</v>
+        <v>91937</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758718</v>
+        <v>758902</v>
       </c>
       <c r="R17" t="n">
-        <v>7176498</v>
+        <v>7176510</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,11 +2338,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2383,42 +2365,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132880932</v>
+        <v>132880236</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>91937</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2426,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758831</v>
+        <v>758722</v>
       </c>
       <c r="R18" t="n">
-        <v>7176561</v>
+        <v>7176524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,17 +2445,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>gammalt bohål i fallen, ihålig gran. typisk storlek och höjd över marken.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2493,42 +2470,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132879963</v>
+        <v>132881150</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>91937</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2536,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>758835</v>
+        <v>758833</v>
       </c>
       <c r="R19" t="n">
-        <v>7176510</v>
+        <v>7176533</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,17 +2550,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2603,42 +2575,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132879227</v>
+        <v>132878955</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2646,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>758894</v>
+        <v>758996</v>
       </c>
       <c r="R20" t="n">
-        <v>7176513</v>
+        <v>7176557</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,17 +2655,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,38 +2680,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132880236</v>
+        <v>132879174</v>
       </c>
       <c r="B21" t="n">
-        <v>91883</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2755,10 +2722,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>758722</v>
+        <v>758921</v>
       </c>
       <c r="R21" t="n">
-        <v>7176524</v>
+        <v>7176542</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,14 +2785,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132878955</v>
+        <v>132879195</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2860,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>758996</v>
+        <v>758892</v>
       </c>
       <c r="R22" t="n">
-        <v>7176557</v>
+        <v>7176540</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,6 +2863,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>riklig förekomst med många draperade träd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2923,38 +2895,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132881237</v>
+        <v>132879548</v>
       </c>
       <c r="B23" t="n">
-        <v>92344</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2965,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>758837</v>
+        <v>758831</v>
       </c>
       <c r="R23" t="n">
-        <v>7176528</v>
+        <v>7176482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,7 +2977,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>rik förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,14 +3005,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132880308</v>
+        <v>132879569</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3075,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>758712</v>
+        <v>758815</v>
       </c>
       <c r="R24" t="n">
-        <v>7176474</v>
+        <v>7176479</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,14 +3110,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132879174</v>
+        <v>132879927</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3180,10 +3152,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>758921</v>
+        <v>758851</v>
       </c>
       <c r="R25" t="n">
-        <v>7176542</v>
+        <v>7176509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,38 +3215,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132880214</v>
+        <v>132880169</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3285,10 +3257,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>758739</v>
+        <v>758769</v>
       </c>
       <c r="R26" t="n">
-        <v>7176545</v>
+        <v>7176522</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,42 +3320,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132879486</v>
+        <v>132880308</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3391,10 +3362,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>758856</v>
+        <v>758712</v>
       </c>
       <c r="R27" t="n">
-        <v>7176478</v>
+        <v>7176474</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,17 +3400,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>färskt ringhack högt upp i tall, observerat med kikare</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3458,42 +3425,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132880065</v>
+        <v>132880331</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3501,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>758817</v>
+        <v>758636</v>
       </c>
       <c r="R28" t="n">
-        <v>7176470</v>
+        <v>7176527</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,17 +3505,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>bohål i gran, typisk höjd över marken och storlek på hålet</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3568,14 +3530,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132879195</v>
+        <v>132880715</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3610,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>758892</v>
+        <v>758712</v>
       </c>
       <c r="R29" t="n">
-        <v>7176540</v>
+        <v>7176550</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3646,11 +3608,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>riklig förekomst med många draperade träd</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3678,38 +3635,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132879679</v>
+        <v>132880736</v>
       </c>
       <c r="B30" t="n">
-        <v>91920</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3720,10 +3677,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>758824</v>
+        <v>758706</v>
       </c>
       <c r="R30" t="n">
-        <v>7176484</v>
+        <v>7176543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,42 +3740,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132880809</v>
+        <v>132881300</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3826,10 +3782,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>758708</v>
+        <v>758875</v>
       </c>
       <c r="R31" t="n">
-        <v>7176532</v>
+        <v>7176545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3866,15 +3822,16 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>rikligt på många träd</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3893,27 +3850,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132881273</v>
+        <v>132880132</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3936,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>758880</v>
+        <v>758797</v>
       </c>
       <c r="R32" t="n">
-        <v>7176534</v>
+        <v>7176492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,14 +3933,14 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackade i träd</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4003,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132879868</v>
+        <v>132878922</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,7 +3993,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4046,10 +4003,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>758849</v>
+        <v>759007</v>
       </c>
       <c r="R33" t="n">
-        <v>7176524</v>
+        <v>7176563</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,14 +4043,14 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>bohål i gran, typisk storlek och ca 180cm över mark</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4113,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132881068</v>
+        <v>132879227</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4156,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>758820</v>
+        <v>758894</v>
       </c>
       <c r="R34" t="n">
-        <v>7176557</v>
+        <v>7176513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,7 +4153,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>barksprätt på gran med granticka</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4223,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132879900</v>
+        <v>132879321</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4266,10 +4223,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758850</v>
+        <v>758878</v>
       </c>
       <c r="R35" t="n">
-        <v>7176510</v>
+        <v>7176445</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4333,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132880262</v>
+        <v>132879462</v>
       </c>
       <c r="B36" t="n">
-        <v>91920</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,30 +4301,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4375,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758718</v>
+        <v>758832</v>
       </c>
       <c r="R36" t="n">
-        <v>7176498</v>
+        <v>7176463</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4413,13 +4371,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4438,10 +4400,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132880221</v>
+        <v>132879486</v>
       </c>
       <c r="B37" t="n">
-        <v>91920</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,30 +4411,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4480,10 +4443,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758724</v>
+        <v>758856</v>
       </c>
       <c r="R37" t="n">
-        <v>7176532</v>
+        <v>7176478</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4518,13 +4481,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>färskt ringhack högt upp i tall, observerat med kikare</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4543,41 +4510,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132879278</v>
+        <v>132879644</v>
       </c>
       <c r="B38" t="n">
-        <v>91883</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4585,10 +4553,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758902</v>
+        <v>758815</v>
       </c>
       <c r="R38" t="n">
-        <v>7176510</v>
+        <v>7176479</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4623,13 +4591,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4648,10 +4620,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132879924</v>
+        <v>132879868</v>
       </c>
       <c r="B39" t="n">
-        <v>91920</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,30 +4631,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4690,10 +4663,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758851</v>
+        <v>758849</v>
       </c>
       <c r="R39" t="n">
-        <v>7176509</v>
+        <v>7176524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4728,13 +4701,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>bohål i gran, typisk storlek och ca 180cm över mark</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4753,10 +4730,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132880963</v>
+        <v>132879900</v>
       </c>
       <c r="B40" t="n">
-        <v>91940</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4764,26 +4741,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4791,10 +4773,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758831</v>
+        <v>758850</v>
       </c>
       <c r="R40" t="n">
-        <v>7176561</v>
+        <v>7176510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4829,13 +4811,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4854,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132879569</v>
+        <v>132879953</v>
       </c>
       <c r="B41" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4865,30 +4851,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4896,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>758815</v>
+        <v>758847</v>
       </c>
       <c r="R41" t="n">
-        <v>7176479</v>
+        <v>7176492</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4934,13 +4921,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4959,10 +4950,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132878922</v>
+        <v>132879963</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5002,10 +4993,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>759007</v>
+        <v>758835</v>
       </c>
       <c r="R42" t="n">
-        <v>7176563</v>
+        <v>7176510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5069,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132879548</v>
+        <v>132880065</v>
       </c>
       <c r="B43" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5080,30 +5071,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5111,10 +5103,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>758831</v>
+        <v>758817</v>
       </c>
       <c r="R43" t="n">
-        <v>7176482</v>
+        <v>7176470</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5151,7 +5143,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>rik förekomst</t>
+          <t>bohål i gran, typisk höjd över marken och storlek på hålet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5160,7 +5152,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5179,10 +5170,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132880169</v>
+        <v>132880152</v>
       </c>
       <c r="B44" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5190,30 +5181,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5221,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>758769</v>
+        <v>758776</v>
       </c>
       <c r="R44" t="n">
-        <v>7176522</v>
+        <v>7176508</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5259,13 +5251,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5284,10 +5280,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132881222</v>
+        <v>132880196</v>
       </c>
       <c r="B45" t="n">
-        <v>91920</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5295,30 +5291,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5326,10 +5323,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>758837</v>
+        <v>758775</v>
       </c>
       <c r="R45" t="n">
-        <v>7176528</v>
+        <v>7176533</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,13 +5361,17 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5389,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132880132</v>
+        <v>132880324</v>
       </c>
       <c r="B46" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5400,16 +5401,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5432,10 +5433,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>758797</v>
+        <v>758646</v>
       </c>
       <c r="R46" t="n">
-        <v>7176492</v>
+        <v>7176522</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5472,14 +5473,14 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>hål hackade i träd</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5499,10 +5500,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132879953</v>
+        <v>132880809</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5542,10 +5543,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>758847</v>
+        <v>758708</v>
       </c>
       <c r="R47" t="n">
-        <v>7176492</v>
+        <v>7176532</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,10 +5610,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132879644</v>
+        <v>132880847</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5652,10 +5653,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>758815</v>
+        <v>758736</v>
       </c>
       <c r="R48" t="n">
-        <v>7176479</v>
+        <v>7176555</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5719,10 +5720,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132880152</v>
+        <v>132880898</v>
       </c>
       <c r="B49" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5762,10 +5763,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>758776</v>
+        <v>758745</v>
       </c>
       <c r="R49" t="n">
-        <v>7176508</v>
+        <v>7176555</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5826,6 +5827,654 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132880932</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>758831</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7176561</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>gammalt bohål i fallen, ihålig gran. typisk storlek och höjd över marken.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132881068</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>758820</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7176557</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>barksprätt på gran med granticka</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132881273</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>758880</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7176534</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132880032</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>758820</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7176502</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132880784</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>758703</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7176533</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132881159</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>758818</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7176529</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14286-2026 artfynd.xlsx
+++ b/artfynd/A 14286-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880345</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879260</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879388</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879679</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879924</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880214</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880221</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880262</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881147</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881175</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881222</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880293</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879887</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881237</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879094</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,6 +2442,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879278</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880236</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2572,6 +2662,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881150</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2677,6 +2772,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878955</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879174</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879195</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3002,6 +3112,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879548</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879569</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3212,6 +3332,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879927</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3317,6 +3442,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880169</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3422,6 +3552,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880308</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3527,6 +3662,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880331</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3632,6 +3772,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880715</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3737,6 +3882,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880736</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3847,6 +3997,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881300</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3957,6 +4112,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880132</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4067,6 +4227,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132878922</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4177,6 +4342,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879227</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4287,6 +4457,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879321</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4397,6 +4572,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879462</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4507,6 +4687,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879486</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4617,6 +4802,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879644</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4727,6 +4917,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879868</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4837,6 +5032,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879900</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4947,6 +5147,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879953</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5057,6 +5262,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132879963</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5167,6 +5377,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880065</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5277,6 +5492,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880152</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5387,6 +5607,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880196</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5497,6 +5722,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880324</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5607,6 +5837,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880809</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5717,6 +5952,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880847</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5827,6 +6067,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880898</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5937,6 +6182,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880932</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6047,6 +6297,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881068</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6157,6 +6412,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881273</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6263,6 +6523,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880032</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6369,6 +6634,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132880784</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6475,8 +6745,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132881159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>